--- a/fde-pre-visit-intake/template/intake_form.xlsx
+++ b/fde-pre-visit-intake/template/intake_form.xlsx
@@ -632,7 +632,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="22" customHeight="1">
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>4</t>
@@ -640,7 +640,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>不确定、不知道的地方空着，我们上门时再一起确认。</t>
+          <t>任何问题都可以跳过，不需要说明原因：不知道的写“不清楚”，不想回答的写“跳过”或直接空着。我们上门时再一起确认。</t>
         </is>
       </c>
     </row>
